--- a/Data/EXCEL/Transfer/dividend/20260225_0_4/8070-dividend-20260225_0_4.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260225_0_4/8070-dividend-20260225_0_4.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260225_0_4\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\20260225_0_4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{EAB182A1-EC5A-4610-881D-830BCE608A70}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{468F603F-B59D-4F31-AA3C-8D0DC327EC5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4140" yWindow="576" windowWidth="16656" windowHeight="10992" xr2:uid="{6E152715-52BF-42A0-BC32-C29FB853E730}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="22845" windowHeight="19530" xr2:uid="{5A8188C0-592B-4F17-888D-9C7DC91D4E57}"/>
   </bookViews>
   <sheets>
     <sheet name="8070-dividend-20260225_0_4" sheetId="1" r:id="rId1"/>
@@ -1505,23 +1505,23 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0F9EF57C-A0F3-403E-B1D6-5698F2AAFE75}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FBD66BDE-310D-4A34-AF6B-35DE1E9587E4}">
   <dimension ref="A1:R45"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.109375" customWidth="1"/>
-    <col min="2" max="2" width="8.77734375" customWidth="1"/>
-    <col min="3" max="3" width="8" customWidth="1"/>
-    <col min="4" max="7" width="8.33203125" customWidth="1"/>
-    <col min="8" max="8" width="8" customWidth="1"/>
-    <col min="9" max="10" width="8.33203125" customWidth="1"/>
-    <col min="11" max="13" width="8" customWidth="1"/>
-    <col min="14" max="14" width="8.33203125" customWidth="1"/>
-    <col min="15" max="17" width="8" customWidth="1"/>
-    <col min="18" max="18" width="8.33203125" customWidth="1"/>
+    <col min="1" max="1" width="6.375" customWidth="1"/>
+    <col min="2" max="2" width="10.875" customWidth="1"/>
+    <col min="3" max="3" width="9.875" customWidth="1"/>
+    <col min="4" max="7" width="10.375" customWidth="1"/>
+    <col min="8" max="8" width="9.875" customWidth="1"/>
+    <col min="9" max="10" width="10.375" customWidth="1"/>
+    <col min="11" max="13" width="9.875" customWidth="1"/>
+    <col min="14" max="14" width="10.375" customWidth="1"/>
+    <col min="15" max="17" width="9.875" customWidth="1"/>
+    <col min="18" max="18" width="11.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A1" s="22" t="s">
         <v>0</v>
       </c>
@@ -1549,7 +1549,7 @@
       <c r="Q1" s="31"/>
       <c r="R1" s="23"/>
     </row>
-    <row r="2" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A2" s="24" t="s">
         <v>1</v>
       </c>
@@ -1579,7 +1579,7 @@
       <c r="Q2" s="33"/>
       <c r="R2" s="34"/>
     </row>
-    <row r="3" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A3" s="24" t="s">
         <v>2</v>
       </c>
@@ -1625,7 +1625,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A4" s="26"/>
       <c r="B4" s="27"/>
       <c r="C4" s="7"/>
@@ -1675,7 +1675,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A5" s="38">
         <v>2025</v>
       </c>
@@ -1729,7 +1729,7 @@
         <v>6.31</v>
       </c>
     </row>
-    <row r="6" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
         <v>25</v>
       </c>
@@ -1785,7 +1785,7 @@
         <v>1.59</v>
       </c>
     </row>
-    <row r="7" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
         <v>25</v>
       </c>
@@ -1841,7 +1841,7 @@
         <v>4.72</v>
       </c>
     </row>
-    <row r="8" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A8" s="40">
         <v>2024</v>
       </c>
@@ -1895,7 +1895,7 @@
         <v>5.62</v>
       </c>
     </row>
-    <row r="9" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A9" s="17" t="s">
         <v>25</v>
       </c>
@@ -1951,7 +1951,7 @@
         <v>1.52</v>
       </c>
     </row>
-    <row r="10" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A10" s="17" t="s">
         <v>25</v>
       </c>
@@ -2007,7 +2007,7 @@
         <v>4.0999999999999996</v>
       </c>
     </row>
-    <row r="11" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A11" s="38">
         <v>2023</v>
       </c>
@@ -2061,7 +2061,7 @@
         <v>6.46</v>
       </c>
     </row>
-    <row r="12" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A12" s="11" t="s">
         <v>25</v>
       </c>
@@ -2117,7 +2117,7 @@
         <v>1.58</v>
       </c>
     </row>
-    <row r="13" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
         <v>25</v>
       </c>
@@ -2173,7 +2173,7 @@
         <v>4.88</v>
       </c>
     </row>
-    <row r="14" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A14" s="40">
         <v>2022</v>
       </c>
@@ -2227,7 +2227,7 @@
         <v>6.68</v>
       </c>
     </row>
-    <row r="15" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A15" s="17" t="s">
         <v>25</v>
       </c>
@@ -2283,7 +2283,7 @@
         <v>2.2799999999999998</v>
       </c>
     </row>
-    <row r="16" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A16" s="17" t="s">
         <v>25</v>
       </c>
@@ -2339,7 +2339,7 @@
         <v>4.4000000000000004</v>
       </c>
     </row>
-    <row r="17" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A17" s="38">
         <v>2021</v>
       </c>
@@ -2393,7 +2393,7 @@
         <v>3.92</v>
       </c>
     </row>
-    <row r="18" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A18" s="11" t="s">
         <v>25</v>
       </c>
@@ -2449,7 +2449,7 @@
         <v>1.1100000000000001</v>
       </c>
     </row>
-    <row r="19" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A19" s="11" t="s">
         <v>25</v>
       </c>
@@ -2505,7 +2505,7 @@
         <v>2.8</v>
       </c>
     </row>
-    <row r="20" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A20" s="40">
         <v>2020</v>
       </c>
@@ -2559,7 +2559,7 @@
         <v>5.98</v>
       </c>
     </row>
-    <row r="21" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A21" s="17" t="s">
         <v>25</v>
       </c>
@@ -2615,7 +2615,7 @@
         <v>0.84</v>
       </c>
     </row>
-    <row r="22" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A22" s="17" t="s">
         <v>25</v>
       </c>
@@ -2671,7 +2671,7 @@
         <v>5.14</v>
       </c>
     </row>
-    <row r="23" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A23" s="38">
         <v>2019</v>
       </c>
@@ -2725,7 +2725,7 @@
         <v>9.27</v>
       </c>
     </row>
-    <row r="24" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A24" s="11" t="s">
         <v>25</v>
       </c>
@@ -2781,7 +2781,7 @@
         <v>2.31</v>
       </c>
     </row>
-    <row r="25" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A25" s="11" t="s">
         <v>25</v>
       </c>
@@ -2837,7 +2837,7 @@
         <v>6.96</v>
       </c>
     </row>
-    <row r="26" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A26" s="40">
         <v>2018</v>
       </c>
@@ -2891,7 +2891,7 @@
         <v>7.38</v>
       </c>
     </row>
-    <row r="27" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A27" s="38">
         <v>2017</v>
       </c>
@@ -2945,7 +2945,7 @@
         <v>6.27</v>
       </c>
     </row>
-    <row r="28" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A28" s="40">
         <v>2016</v>
       </c>
@@ -2999,7 +2999,7 @@
         <v>7.78</v>
       </c>
     </row>
-    <row r="29" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A29" s="38">
         <v>2015</v>
       </c>
@@ -3053,7 +3053,7 @@
         <v>3.38</v>
       </c>
     </row>
-    <row r="30" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A30" s="40">
         <v>2014</v>
       </c>
@@ -3107,7 +3107,7 @@
         <v>3.69</v>
       </c>
     </row>
-    <row r="31" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A31" s="38">
         <v>2013</v>
       </c>
@@ -3161,7 +3161,7 @@
         <v>3.54</v>
       </c>
     </row>
-    <row r="32" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A32" s="40">
         <v>2012</v>
       </c>
@@ -3215,7 +3215,7 @@
         <v>1.37</v>
       </c>
     </row>
-    <row r="33" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A33" s="38">
         <v>2011</v>
       </c>
@@ -3269,7 +3269,7 @@
         <v>8.06</v>
       </c>
     </row>
-    <row r="34" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A34" s="40">
         <v>2010</v>
       </c>
@@ -3323,7 +3323,7 @@
         <v>3.67</v>
       </c>
     </row>
-    <row r="35" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A35" s="38">
         <v>2009</v>
       </c>
@@ -3377,7 +3377,7 @@
         <v>3.67</v>
       </c>
     </row>
-    <row r="36" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A36" s="40">
         <v>2008</v>
       </c>
@@ -3431,7 +3431,7 @@
         <v>7.53</v>
       </c>
     </row>
-    <row r="37" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A37" s="38">
         <v>2007</v>
       </c>
@@ -3485,7 +3485,7 @@
         <v>3.92</v>
       </c>
     </row>
-    <row r="38" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A38" s="40">
         <v>2006</v>
       </c>
@@ -3539,7 +3539,7 @@
         <v>4.09</v>
       </c>
     </row>
-    <row r="39" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A39" s="38">
         <v>2005</v>
       </c>
@@ -3593,7 +3593,7 @@
         <v>5.45</v>
       </c>
     </row>
-    <row r="40" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A40" s="40">
         <v>2004</v>
       </c>
@@ -3647,7 +3647,7 @@
         <v>4.67</v>
       </c>
     </row>
-    <row r="41" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A41" s="38">
         <v>2003</v>
       </c>
@@ -3701,7 +3701,7 @@
         <v>3.7</v>
       </c>
     </row>
-    <row r="42" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A42" s="40">
         <v>2002</v>
       </c>
@@ -3755,7 +3755,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="43" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A43" s="38">
         <v>2001</v>
       </c>
@@ -3809,7 +3809,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="44" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A44" s="40">
         <v>2000</v>
       </c>
@@ -3863,7 +3863,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="45" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A45" s="38" t="s">
         <v>53</v>
       </c>
